--- a/evaluation/static_checking/report/DeepEval/gpt_4o/gpt_4o.xlsx
+++ b/evaluation/static_checking/report/DeepEval/gpt_4o/gpt_4o.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxy/Documents/pythonProject/my_experiemnt/model-level-testing/DeepEval/evaluation/syntatic_checking/report/DeepEval/gpt_4o/total/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxy/Documents/文档资料/个人资料/我的成果/DeepEval-artifacts/source_code/DeepEval_DeepEval/DeepEval/evaluation/static_checking/report/DeepEval/gpt_4o/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9976C10A-9417-4040-AAC7-0D96824E146E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E366B6-5BA0-7446-88DC-D23DC7478C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="zeroshot1" sheetId="7" r:id="rId1"/>
-    <sheet name="oneshot1" sheetId="8" r:id="rId2"/>
-    <sheet name="oneshotcot1" sheetId="9" r:id="rId3"/>
-    <sheet name="fewshot1" sheetId="10" r:id="rId4"/>
-    <sheet name="summary1" sheetId="11" r:id="rId5"/>
-    <sheet name="total_summary1" sheetId="12" r:id="rId6"/>
+    <sheet name="zeroshot" sheetId="7" r:id="rId1"/>
+    <sheet name="oneshot" sheetId="8" r:id="rId2"/>
+    <sheet name="oneshotcot" sheetId="9" r:id="rId3"/>
+    <sheet name="fewshot" sheetId="10" r:id="rId4"/>
+    <sheet name="summary" sheetId="11" r:id="rId5"/>
+    <sheet name="total_summary" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
